--- a/plantilla-catalogo.xlsx
+++ b/plantilla-catalogo.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="31">
   <si>
     <t>nombre</t>
   </si>
@@ -33,6 +33,12 @@
     <t>precio</t>
   </si>
   <si>
+    <t>precio_mayorista</t>
+  </si>
+  <si>
+    <t>cantidad_mayorista</t>
+  </si>
+  <si>
     <t>stock</t>
   </si>
   <si>
@@ -61,6 +67,12 @@
   </si>
   <si>
     <t>- precio: solo el número, sin el signo $. Acepta decimales con coma (ej: 3500 o 3500,50).</t>
+  </si>
+  <si>
+    <t>- precio_mayorista: el precio para clientes mayoristas. Lo pagan siempre los clientes registrados como negocio. Dejalo vacío si no vendés por mayor.</t>
+  </si>
+  <si>
+    <t>- cantidad_mayorista: si además querés que CUALQUIER cliente pague el precio por mayor al llevar cierta cantidad, poné ese número (ej: 6). Vacío = solo los negocios.</t>
   </si>
   <si>
     <t>- sin_tacc / congelado / nuevo: poné "si" cuando corresponda, o dejá vacío. Si tu rubro no es de alimentos, ignorá esas columnas.</t>
@@ -446,21 +458,23 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="true" style="0"/>
     <col min="2" max="2" width="20" customWidth="true" style="0"/>
     <col min="3" max="3" width="20" customWidth="true" style="0"/>
-    <col min="4" max="4" width="14" customWidth="true" style="0"/>
-    <col min="5" max="5" width="14" customWidth="true" style="0"/>
-    <col min="6" max="6" width="14" customWidth="true" style="0"/>
-    <col min="7" max="7" width="14" customWidth="true" style="0"/>
-    <col min="8" max="8" width="14" customWidth="true" style="0"/>
-    <col min="9" max="9" width="14" customWidth="true" style="0"/>
+    <col min="4" max="4" width="16" customWidth="true" style="0"/>
+    <col min="5" max="5" width="16" customWidth="true" style="0"/>
+    <col min="6" max="6" width="16" customWidth="true" style="0"/>
+    <col min="7" max="7" width="16" customWidth="true" style="0"/>
+    <col min="8" max="8" width="16" customWidth="true" style="0"/>
+    <col min="9" max="9" width="16" customWidth="true" style="0"/>
+    <col min="10" max="10" width="16" customWidth="true" style="0"/>
+    <col min="11" max="11" width="16" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -487,6 +501,12 @@
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -510,159 +530,189 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="true" style="0"/>
-    <col min="2" max="2" width="14" customWidth="true" style="0"/>
-    <col min="3" max="3" width="14" customWidth="true" style="0"/>
-    <col min="4" max="4" width="14" customWidth="true" style="0"/>
-    <col min="5" max="5" width="14" customWidth="true" style="0"/>
-    <col min="6" max="6" width="14" customWidth="true" style="0"/>
-    <col min="7" max="7" width="14" customWidth="true" style="0"/>
-    <col min="8" max="8" width="14" customWidth="true" style="0"/>
-    <col min="9" max="9" width="14" customWidth="true" style="0"/>
+    <col min="2" max="2" width="16" customWidth="true" style="0"/>
+    <col min="3" max="3" width="16" customWidth="true" style="0"/>
+    <col min="4" max="4" width="16" customWidth="true" style="0"/>
+    <col min="5" max="5" width="16" customWidth="true" style="0"/>
+    <col min="6" max="6" width="16" customWidth="true" style="0"/>
+    <col min="7" max="7" width="16" customWidth="true" style="0"/>
+    <col min="8" max="8" width="16" customWidth="true" style="0"/>
+    <col min="9" max="9" width="16" customWidth="true" style="0"/>
+    <col min="10" max="10" width="16" customWidth="true" style="0"/>
+    <col min="11" max="11" width="16" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
+      <c r="K14" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="1" t="s">
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15">
+        <v>3500</v>
+      </c>
+      <c r="F15">
+        <v>3100</v>
+      </c>
+      <c r="G15">
+        <v>6</v>
+      </c>
+      <c r="H15">
+        <v>10</v>
+      </c>
+      <c r="I15" t="s">
+        <v>25</v>
+      </c>
+      <c r="K15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16">
+        <v>6500</v>
+      </c>
+      <c r="F16">
+        <v>5900</v>
+      </c>
+      <c r="G16">
+        <v>6</v>
+      </c>
+      <c r="H16">
         <v>5</v>
       </c>
-      <c r="G12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I12" s="1" t="s">
+      <c r="I16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17">
+        <v>4200</v>
+      </c>
+      <c r="H17">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13">
-        <v>3500</v>
-      </c>
-      <c r="F13">
-        <v>10</v>
-      </c>
-      <c r="G13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" t="s">
-        <v>19</v>
-      </c>
-      <c r="D14" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14">
-        <v>6500</v>
-      </c>
-      <c r="F14">
-        <v>5</v>
-      </c>
-      <c r="G14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="J17" t="s">
         <v>25</v>
-      </c>
-      <c r="D15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15">
-        <v>4200</v>
-      </c>
-      <c r="F15">
-        <v>8</v>
-      </c>
-      <c r="H15" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/plantilla-catalogo.xlsx
+++ b/plantilla-catalogo.xlsx
@@ -1,14 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Productos" sheetId="1" r:id="rId4"/>
-    <sheet name="Como llenar" sheetId="2" r:id="rId5"/>
+    <sheet name="Catálogo" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -16,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="18">
   <si>
     <t>nombre</t>
   </si>
@@ -42,79 +41,40 @@
     <t>stock</t>
   </si>
   <si>
-    <t>sin_tacc</t>
-  </si>
-  <si>
-    <t>congelado</t>
+    <t>etiquetas</t>
   </si>
   <si>
     <t>nuevo</t>
   </si>
   <si>
-    <t>CÓMO LLENAR LA PLANILLA</t>
-  </si>
-  <si>
-    <t>- Cargá tus productos en la hoja "Productos", debajo de los títulos. No cambies los títulos.</t>
-  </si>
-  <si>
-    <t>- Una fila por producto y por presentación: si el mismo producto viene en dos tamaños, van dos filas con el mismo nombre y la misma marca.</t>
-  </si>
-  <si>
-    <t>- Obligatorios: nombre y marca. El resto se puede dejar vacío.</t>
-  </si>
-  <si>
-    <t>- Si tus productos no tienen marca, poné el nombre de tu negocio como marca.</t>
-  </si>
-  <si>
-    <t>- precio: solo el número, sin el signo $. Acepta decimales con coma (ej: 3500 o 3500,50).</t>
-  </si>
-  <si>
-    <t>- precio_mayorista: el precio para clientes mayoristas. Lo pagan siempre los clientes registrados como negocio. Dejalo vacío si no vendés por mayor.</t>
-  </si>
-  <si>
-    <t>- cantidad_mayorista: si además querés que CUALQUIER cliente pague el precio por mayor al llevar cierta cantidad, poné ese número (ej: 6). Vacío = solo los negocios.</t>
-  </si>
-  <si>
-    <t>- sin_tacc / congelado / nuevo: poné "si" cuando corresponda, o dejá vacío. Si tu rubro no es de alimentos, ignorá esas columnas.</t>
-  </si>
-  <si>
-    <t>EJEMPLO (así se ve una carga correcta):</t>
-  </si>
-  <si>
-    <t>Yerba orgánica</t>
-  </si>
-  <si>
-    <t>Marca Ejemplo</t>
-  </si>
-  <si>
-    <t>Almacén</t>
-  </si>
-  <si>
-    <t>500g</t>
+    <t>Miel de eucalipto</t>
+  </si>
+  <si>
+    <t>Mi Marca</t>
+  </si>
+  <si>
+    <t>Mieles</t>
+  </si>
+  <si>
+    <t>500 g</t>
+  </si>
+  <si>
+    <t>Sin TACC, Artesanal</t>
+  </si>
+  <si>
+    <t>Miel de trébol</t>
+  </si>
+  <si>
+    <t>1 kg</t>
   </si>
   <si>
     <t>si</t>
-  </si>
-  <si>
-    <t>1kg</t>
-  </si>
-  <si>
-    <t>Hamburguesas de lenteja</t>
-  </si>
-  <si>
-    <t>La Huerta</t>
-  </si>
-  <si>
-    <t>Congelados</t>
-  </si>
-  <si>
-    <t>x4</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="2">
     <font>
@@ -136,12 +96,18 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDE9E1"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -158,7 +124,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -454,27 +420,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="true" style="0"/>
-    <col min="2" max="2" width="20" customWidth="true" style="0"/>
-    <col min="3" max="3" width="20" customWidth="true" style="0"/>
-    <col min="4" max="4" width="16" customWidth="true" style="0"/>
-    <col min="5" max="5" width="16" customWidth="true" style="0"/>
-    <col min="6" max="6" width="16" customWidth="true" style="0"/>
-    <col min="7" max="7" width="16" customWidth="true" style="0"/>
-    <col min="8" max="8" width="16" customWidth="true" style="0"/>
-    <col min="9" max="9" width="16" customWidth="true" style="0"/>
-    <col min="10" max="10" width="16" customWidth="true" style="0"/>
-    <col min="11" max="11" width="16" customWidth="true" style="0"/>
+    <col min="1" max="1" width="21.138" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="19.995" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="22.28" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="23.423" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="6.998" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -505,228 +470,62 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
         <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2">
+        <v>7500</v>
+      </c>
+      <c r="F2">
+        <v>6400</v>
+      </c>
+      <c r="G2">
+        <v>6</v>
+      </c>
+      <c r="H2">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3">
+        <v>14500</v>
+      </c>
+      <c r="H3">
+        <v>12</v>
+      </c>
+      <c r="J3" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-  </sheetPr>
-  <dimension ref="A1:K17"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col min="1" max="1" width="34" customWidth="true" style="0"/>
-    <col min="2" max="2" width="16" customWidth="true" style="0"/>
-    <col min="3" max="3" width="16" customWidth="true" style="0"/>
-    <col min="4" max="4" width="16" customWidth="true" style="0"/>
-    <col min="5" max="5" width="16" customWidth="true" style="0"/>
-    <col min="6" max="6" width="16" customWidth="true" style="0"/>
-    <col min="7" max="7" width="16" customWidth="true" style="0"/>
-    <col min="8" max="8" width="16" customWidth="true" style="0"/>
-    <col min="9" max="9" width="16" customWidth="true" style="0"/>
-    <col min="10" max="10" width="16" customWidth="true" style="0"/>
-    <col min="11" max="11" width="16" customWidth="true" style="0"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D15" t="s">
-        <v>24</v>
-      </c>
-      <c r="E15">
-        <v>3500</v>
-      </c>
-      <c r="F15">
-        <v>3100</v>
-      </c>
-      <c r="G15">
-        <v>6</v>
-      </c>
-      <c r="H15">
-        <v>10</v>
-      </c>
-      <c r="I15" t="s">
-        <v>25</v>
-      </c>
-      <c r="K15" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" t="s">
-        <v>23</v>
-      </c>
-      <c r="D16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16">
-        <v>6500</v>
-      </c>
-      <c r="F16">
-        <v>5900</v>
-      </c>
-      <c r="G16">
-        <v>6</v>
-      </c>
-      <c r="H16">
-        <v>5</v>
-      </c>
-      <c r="I16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17">
-        <v>4200</v>
-      </c>
-      <c r="H17">
-        <v>8</v>
-      </c>
-      <c r="J17" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions gridLines="false" gridLinesSet="true"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
-  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
-    <oddHeader/>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-  <tableParts count="0"/>
 </worksheet>
 </file>